--- a/Cred1.xlsx
+++ b/Cred1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7d1ab83e58f3f6fd/Documentos/PUCE/Master Finanzas/Masterclass/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{7731DED7-8801-4C07-B400-894B584C787C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E4A011D-3DE0-4009-9EE9-0402449CE0EE}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{7731DED7-8801-4C07-B400-894B584C787C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{025B6063-5570-4416-A2C2-16A5F57175F2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F55F4B6-6048-4A52-98DB-C2FF5EE0DB43}"/>
   </bookViews>
@@ -16,8 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$B$1</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$B$2:$B$2952</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$2952</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32987,6 +32986,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="C1:C2952" xr:uid="{6848A643-4F61-45E9-98EC-5510E99E3D66}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>